--- a/Docs/buro_credito.xlsx
+++ b/Docs/buro_credito.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,2256 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CLI-1006</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>710</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CLI-1007</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>680</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CLI-1008</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>590</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CLI-1009</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>750</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CLI-1010</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>640</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CLI-1011</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>700</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CLI-1012</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>601</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cliente_1013</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>600</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CLI-1014</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>820</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CLI-1015</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>665</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CLI-1016</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>690</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CLI-1017</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>775</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CLI-1018</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>560</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CLI-1019</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>705</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CLI-1020</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>640</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CLI-1021</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>615</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CLI-1022</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>630</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CLI-1023</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>720</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CLI-1024</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>660</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CLI-1025</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>810</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cliente_1026</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>545</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CLI-1027</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>610</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CLI-1028</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>700</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CLI-1030</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>690</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CLI-1031</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>650</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CLI-1032</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>600</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CLI-1033</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>620</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>CLI-1034</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>790</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CLI-1035</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>680</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>CLI-1036</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>800</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CLI-1037</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>729</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CLI-1038</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>559</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CLI-1039</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>572</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CLI-1040</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>661</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CLI-1041</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>587</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CLI-1042</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>773</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CLI-1043</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>601</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CLI-1044</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>741</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CLI-1045</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>667</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CLI-1046</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>699</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CLI-1047</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>600</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CLI-1048</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>531</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CLI-1049</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>633</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CLI-1050</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>566</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CLI-1051</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>494</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CLIENTE_1052</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>601</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CLI-1053</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>400</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CLI-1054</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>594</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>CLI-1055</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>600</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>CLI-1056</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>654</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>CLI-1057</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>708</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>CLI-1058</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>649</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>CLI-1059</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>656</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CLI-1060</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>681</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>CLI-1061</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>850</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>CLI-1062</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>648</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>CLI-1063</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>730</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>CLI-1064</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>479</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CLI-1065</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>539</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CLI-1066</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>634</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>CLI-1067</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>525</v>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>CLI-1068</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>626</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>CLI-1069</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>577</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>CLI-1070</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>624</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>CLI-1073</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>833</v>
+      </c>
+      <c r="C70" t="n">
+        <v>3</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CLI-1074</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>737</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CLI-1075</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>562</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>CLI-1076</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>616</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CLI-1077</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>718</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CLI-1078</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>746</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>CLI-1079</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>565</v>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>CLI-1080</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>730</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CLI-1081</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>698</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>CLI-1082</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>566</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>CLI-1083</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>676</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CLI-1084</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>601</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CLI-1085</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>705</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CLI-1086</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>642</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CLI-1087</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>671</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CLI-1088</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>533</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CLI-1089</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>546</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CLI-1090</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>729</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CLI-1091</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>692</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CLI-1092</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>631</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CLI-1093</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>792</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CLI-1094</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>601</v>
+      </c>
+      <c r="C91" t="n">
+        <v>5</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CLI-1095</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>648</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CLI-1096</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>587</v>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CLI-1097</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>668</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CLI-1099</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>629</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CLI-1100</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>731</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CLI-1101</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>652</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CLI-1102</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>706</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CLI-1103</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>534</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CLI-1104</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>629</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CLI-1105</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>581</v>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CLIENTE_1106</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>648</v>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>CLI-1107</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>618</v>
+      </c>
+      <c r="C103" t="n">
+        <v>4</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>CLI-1108</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>562</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CLI-1109</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>528</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>CLI-1110</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>596</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>CLI-1111</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>710</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>CLI-1112</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>578</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>CLI-1113</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>664</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CLI-1114</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>711</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CLI-1115</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>652</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CLI-1116</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>693</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CLI-1117</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>530</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CLI-1118</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>745</v>
+      </c>
+      <c r="C114" t="n">
+        <v>5</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CLI-1120</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>567</v>
+      </c>
+      <c r="C115" t="n">
+        <v>5</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CLI-1121</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>584</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CLIENTE_1122</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>665</v>
+      </c>
+      <c r="C117" t="n">
+        <v>5</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CLI-1123</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>633</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CLI-1124</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>732</v>
+      </c>
+      <c r="C119" t="n">
+        <v>5</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CLI-1125</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>696</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CLI-1126</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>554</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>si</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CLI-1127</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>669</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CLI-1128</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>618</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CLI-1129</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>598</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CLI-1130</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>600</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CLI-1131</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>523</v>
+      </c>
+      <c r="C126" t="n">
+        <v>2</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CLI-1132</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>563</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CLI-1133</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>720</v>
+      </c>
+      <c r="C128" t="n">
+        <v>5</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CLI-1134</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>601</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CLI-1135</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>704</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
